--- a/branches/release/2027.0.0-ballot/StructureDefinition-mii-pr-symptom-observation.xlsx
+++ b/branches/release/2027.0.0-ballot/StructureDefinition-mii-pr-symptom-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:17:54+00:00</t>
+    <t>2026-09-11T09:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
